--- a/results/4_runtimes.xlsx
+++ b/results/4_runtimes.xlsx
@@ -575,6 +575,9 @@
       <c r="B2">
         <v>0.02</v>
       </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -601,6 +604,9 @@
       </c>
       <c r="B5">
         <v>0.01</v>
+      </c>
+      <c r="C5">
+        <v>0.86</v>
       </c>
     </row>
     <row r="6" spans="1:3">
